--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/cirno_modifiers.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/cirno_modifiers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D691F86D-0B0B-46F9-9A13-ADD3A0F3FB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F124F714-5436-443A-80B6-D581A7700292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7545" yWindow="2115" windowWidth="19395" windowHeight="12360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="modifiers" sheetId="7" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="19">
   <si>
     <t>Attribute Type</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -52,6 +52,39 @@
   <si>
     <t>Flat/PercentAdd/PercentMul</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동속도 0.02 증가</t>
+  </si>
+  <si>
+    <t>이동속도 0.03 증가</t>
+  </si>
+  <si>
+    <t>이동속도 0.04 증가</t>
+  </si>
+  <si>
+    <t>이동속도 0.05 증가</t>
+  </si>
+  <si>
+    <t>이동속도 0.06 증가</t>
+  </si>
+  <si>
+    <t>이동속도 0.07 증가</t>
+  </si>
+  <si>
+    <t>이동속도 0.08 증가</t>
+  </si>
+  <si>
+    <t>이동속도 0.09 증가</t>
+  </si>
+  <si>
+    <t>이동속도 0.10 증가</t>
+  </si>
+  <si>
+    <t>이동속도 0.11 증가</t>
+  </si>
+  <si>
+    <t>이동속도 0.12 증가</t>
   </si>
 </sst>
 </file>
@@ -373,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3CE5BFE-EF2D-4BBF-853C-AFB047A960B0}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24.625" customWidth="1"/>
@@ -730,14 +763,349 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <v>0.01</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>0.01</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>0.01</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>24</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <v>0.01</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>25</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>0.01</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>26</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26">
+        <v>0.01</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>27</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>0.01</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>28</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28">
+        <v>0.01</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>29</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29">
+        <v>0.01</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>30</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30">
+        <v>1.01</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>31</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>32</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32">
+        <v>3.01</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>33</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33">
+        <v>4.01</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>34</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34">
+        <v>5.01</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>35</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35">
+        <v>6.01</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>36</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36">
+        <v>7.01</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>37</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37">
+        <v>8.01</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>38</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38">
+        <v>9.01</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>39</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39">
+        <v>10.01</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>40</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40">
+        <v>11.01</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
